--- a/output/tables/manuscript/s6_table_effects_by_food_group.xlsx
+++ b/output/tables/manuscript/s6_table_effects_by_food_group.xlsx
@@ -69,7 +69,7 @@
     <t>1.9</t>
   </si>
   <si>
-    <t>(-0.0, 3.8)</t>
+    <t>(-0.03, 3.8)</t>
   </si>
   <si>
     <t>5.2</t>
@@ -168,10 +168,10 @@
     <t>-0.4</t>
   </si>
   <si>
-    <t>(-0.8, 0.0)</t>
-  </si>
-  <si>
-    <t>0.0</t>
+    <t>(-0.8, 0.04)</t>
+  </si>
+  <si>
+    <t>0.03</t>
   </si>
   <si>
     <t>(-0.4, 0.5)</t>
@@ -222,7 +222,7 @@
     <t>(-1.7, -0.2)</t>
   </si>
   <si>
-    <t>(-1.4, 0.0)</t>
+    <t>(-1.4, 0.05)</t>
   </si>
   <si>
     <t>-2.7</t>
@@ -231,7 +231,7 @@
     <t>(-4.3, -1.0)</t>
   </si>
   <si>
-    <t>-0.0</t>
+    <t>-0.01</t>
   </si>
   <si>
     <t>(-1.6, 1.6)</t>
